--- a/excel_db/expenses.xlsx
+++ b/excel_db/expenses.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>id</t>
   </si>
@@ -35,6 +35,45 @@
   </si>
   <si>
     <t>created_at</t>
+  </si>
+  <si>
+    <t>vendor</t>
+  </si>
+  <si>
+    <t>approved_by</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>for water bill</t>
+  </si>
+  <si>
+    <t>src</t>
+  </si>
+  <si>
+    <t>Utilities</t>
+  </si>
+  <si>
+    <t>Cleaning</t>
+  </si>
+  <si>
+    <t>2026-06-07 01:42:21</t>
+  </si>
+  <si>
+    <t>2026-06-07 01:54:56</t>
+  </si>
+  <si>
+    <t>Ghana water</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>Principal</t>
+  </si>
+  <si>
+    <t>issued receipt urgently</t>
   </si>
 </sst>
 </file>
@@ -392,10 +431,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -416,6 +455,64 @@
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>1100</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>500</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
